--- a/data_lake/datos_diarios_preliminares/dt=2026-07-24/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-24/temperaturamed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B7D5E2-9601-434D-9EE2-40515CC61DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F31020-2FF0-4F1B-898D-D6E40BC4200C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Temperatura" sheetId="1" r:id="rId1"/>
@@ -6354,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="109" width="32.42578125" style="50" customWidth="1"/>
-    <col min="110" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="110" width="32.42578125" style="50" customWidth="1"/>
+    <col min="111" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6704,7 +6704,9 @@
       <c r="AF5" s="56">
         <v>28.8</v>
       </c>
-      <c r="AG5" s="56"/>
+      <c r="AG5" s="56">
+        <v>29.2</v>
+      </c>
       <c r="AH5" s="56"/>
       <c r="AI5" s="56"/>
       <c r="AJ5" s="56"/>
@@ -6715,11 +6717,11 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>28.831818181818178</v>
+        <v>28.847826086956523</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6727,7 +6729,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>0.67860329284690835</v>
+        <v>0.69461119798525317</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6827,7 +6829,9 @@
       <c r="AF6" s="56">
         <v>29.3</v>
       </c>
-      <c r="AG6" s="56"/>
+      <c r="AG6" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AH6" s="56"/>
       <c r="AI6" s="56"/>
       <c r="AJ6" s="56"/>
@@ -6838,11 +6842,11 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.877272727272725</v>
+        <v>28.873913043478257</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6850,7 +6854,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>0.48203883832390559</v>
+        <v>0.47867915452943777</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6950,7 +6954,9 @@
       <c r="AF7" s="56">
         <v>32.1</v>
       </c>
-      <c r="AG7" s="56"/>
+      <c r="AG7" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AH7" s="56"/>
       <c r="AI7" s="56"/>
       <c r="AJ7" s="56"/>
@@ -6961,11 +6967,11 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>31.668181818181822</v>
+        <v>31.57826086956522</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6973,7 +6979,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.4680013266303611</v>
+        <v>2.3780803780137596</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7073,7 +7079,9 @@
       <c r="AF8" s="56">
         <v>29.2</v>
       </c>
-      <c r="AG8" s="56"/>
+      <c r="AG8" s="56">
+        <v>28.6</v>
+      </c>
       <c r="AH8" s="56"/>
       <c r="AI8" s="56"/>
       <c r="AJ8" s="56"/>
@@ -7084,11 +7092,11 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>29.831818181818186</v>
+        <v>29.778260869565223</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7096,7 +7104,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.2532788656467844</v>
+        <v>1.1997215533938217</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7196,7 +7204,9 @@
       <c r="AF9" s="56">
         <v>29.1</v>
       </c>
-      <c r="AG9" s="56"/>
+      <c r="AG9" s="56">
+        <v>29.1</v>
+      </c>
       <c r="AH9" s="56"/>
       <c r="AI9" s="56"/>
       <c r="AJ9" s="56"/>
@@ -7207,11 +7217,11 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.436363636363637</v>
+        <v>29.421739130434784</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7219,7 +7229,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>-0.35110534626659273</v>
+        <v>-0.36572985219544663</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7319,7 +7329,9 @@
       <c r="AF10" s="56">
         <v>30</v>
       </c>
-      <c r="AG10" s="56"/>
+      <c r="AG10" s="56">
+        <v>31</v>
+      </c>
       <c r="AH10" s="56"/>
       <c r="AI10" s="56"/>
       <c r="AJ10" s="56"/>
@@ -7330,11 +7342,11 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>31.768181818181816</v>
+        <v>31.734782608695649</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7342,7 +7354,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.6887597837767565</v>
+        <v>1.6553605742905901</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7442,7 +7454,9 @@
       <c r="AF11" s="56">
         <v>31.7</v>
       </c>
-      <c r="AG11" s="56"/>
+      <c r="AG11" s="56">
+        <v>30</v>
+      </c>
       <c r="AH11" s="56"/>
       <c r="AI11" s="56"/>
       <c r="AJ11" s="56"/>
@@ -7453,11 +7467,11 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>32.790909090909089</v>
+        <v>32.669565217391302</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7465,7 +7479,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>2.7869950136812385</v>
+        <v>2.6656511401634511</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7565,7 +7579,9 @@
       <c r="AF12" s="56">
         <v>30.5</v>
       </c>
-      <c r="AG12" s="56"/>
+      <c r="AG12" s="56">
+        <v>25.8</v>
+      </c>
       <c r="AH12" s="56"/>
       <c r="AI12" s="56"/>
       <c r="AJ12" s="56"/>
@@ -7576,11 +7592,11 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>30.318181818181813</v>
+        <v>30.121739130434776</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7588,7 +7604,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>2.0525154288662328</v>
+        <v>1.8560727411191955</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7688,7 +7704,9 @@
       <c r="AF13" s="56">
         <v>29.9</v>
       </c>
-      <c r="AG13" s="56"/>
+      <c r="AG13" s="56">
+        <v>26.9</v>
+      </c>
       <c r="AH13" s="56"/>
       <c r="AI13" s="56"/>
       <c r="AJ13" s="56"/>
@@ -7699,11 +7717,11 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>30.090909090909086</v>
+        <v>29.952173913043474</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7711,7 +7729,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>1.761514393096725</v>
+        <v>1.6227792152311125</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7811,7 +7829,9 @@
       <c r="AF14" s="56">
         <v>24.7</v>
       </c>
-      <c r="AG14" s="56"/>
+      <c r="AG14" s="56">
+        <v>21.9</v>
+      </c>
       <c r="AH14" s="56"/>
       <c r="AI14" s="56"/>
       <c r="AJ14" s="56"/>
@@ -7822,11 +7842,11 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.75454545454545</v>
+        <v>23.673913043478255</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7834,7 +7854,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>2.0330054306506007</v>
+        <v>1.9523730195834048</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7934,7 +7954,9 @@
       <c r="AF15" s="56">
         <v>31.3</v>
       </c>
-      <c r="AG15" s="56"/>
+      <c r="AG15" s="56">
+        <v>28.1</v>
+      </c>
       <c r="AH15" s="56"/>
       <c r="AI15" s="56"/>
       <c r="AJ15" s="56"/>
@@ -7945,11 +7967,11 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.136363636363637</v>
+        <v>29.091304347826089</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7957,7 +7979,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>0.90085826001955738</v>
+        <v>0.85579897148200956</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8057,7 +8079,9 @@
       <c r="AF16" s="56">
         <v>29</v>
       </c>
-      <c r="AG16" s="56"/>
+      <c r="AG16" s="56">
+        <v>24.6</v>
+      </c>
       <c r="AH16" s="56"/>
       <c r="AI16" s="56"/>
       <c r="AJ16" s="56"/>
@@ -8068,11 +8092,11 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.518181818181816</v>
+        <v>28.347826086956523</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8080,7 +8104,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.88052896977883677</v>
+        <v>0.71017323855354419</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8180,7 +8204,9 @@
       <c r="AF17" s="56">
         <v>23.6</v>
       </c>
-      <c r="AG17" s="56"/>
+      <c r="AG17" s="56">
+        <v>21.4</v>
+      </c>
       <c r="AH17" s="56"/>
       <c r="AI17" s="56"/>
       <c r="AJ17" s="56"/>
@@ -8191,11 +8217,11 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>24.818181818181824</v>
+        <v>24.669565217391309</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8203,7 +8229,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.83455814902562508</v>
+        <v>0.68594154823511033</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8303,7 +8329,9 @@
       <c r="AF18" s="56">
         <v>18.600000000000001</v>
       </c>
-      <c r="AG18" s="56"/>
+      <c r="AG18" s="56">
+        <v>18.600000000000001</v>
+      </c>
       <c r="AH18" s="56"/>
       <c r="AI18" s="56"/>
       <c r="AJ18" s="56"/>
@@ -8314,11 +8342,11 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.754545454545454</v>
+        <v>18.747826086956525</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8326,7 +8354,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.3361942000651723</v>
+        <v>1.3294748324762438</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8426,7 +8454,9 @@
       <c r="AF19" s="56">
         <v>25.2</v>
       </c>
-      <c r="AG19" s="56"/>
+      <c r="AG19" s="56">
+        <v>21.9</v>
+      </c>
       <c r="AH19" s="56"/>
       <c r="AI19" s="56"/>
       <c r="AJ19" s="56"/>
@@ -8437,11 +8467,11 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.486363636363638</v>
+        <v>24.373913043478261</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8449,7 +8479,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.3528286901270867</v>
+        <v>2.2403780972417096</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8549,7 +8579,9 @@
       <c r="AF20" s="56">
         <v>22.4</v>
       </c>
-      <c r="AG20" s="56"/>
+      <c r="AG20" s="56">
+        <v>23.4</v>
+      </c>
       <c r="AH20" s="56"/>
       <c r="AI20" s="56"/>
       <c r="AJ20" s="56"/>
@@ -8560,11 +8592,11 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>24.313636363636363</v>
+        <v>24.27391304347826</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8572,7 +8604,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>1.7059709376644925</v>
+        <v>1.6662476175063894</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8672,7 +8704,9 @@
       <c r="AF21" s="56">
         <v>28.5</v>
       </c>
-      <c r="AG21" s="56"/>
+      <c r="AG21" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AH21" s="56"/>
       <c r="AI21" s="56"/>
       <c r="AJ21" s="56"/>
@@ -8683,11 +8717,11 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>27.181818181818183</v>
+        <v>27.143478260869564</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8695,7 +8729,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>2.491736290061052</v>
+        <v>2.4533963691124328</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8795,7 +8829,9 @@
       <c r="AF22" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="AG22" s="56"/>
+      <c r="AG22" s="56">
+        <v>14.9</v>
+      </c>
       <c r="AH22" s="56"/>
       <c r="AI22" s="56"/>
       <c r="AJ22" s="56"/>
@@ -8806,11 +8842,11 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.527272727272726</v>
+        <v>15.499999999999998</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8818,7 +8854,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.7469398075043259</v>
+        <v>1.7196670802315985</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8918,7 +8954,9 @@
       <c r="AF23" s="56">
         <v>26.5</v>
       </c>
-      <c r="AG23" s="56"/>
+      <c r="AG23" s="56">
+        <v>25.1</v>
+      </c>
       <c r="AH23" s="56"/>
       <c r="AI23" s="56"/>
       <c r="AJ23" s="56"/>
@@ -8929,11 +8967,11 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.190909090909084</v>
+        <v>26.143478260869557</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9041,7 +9079,9 @@
       <c r="AF24" s="56">
         <v>30.6</v>
       </c>
-      <c r="AG24" s="56"/>
+      <c r="AG24" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AH24" s="56"/>
       <c r="AI24" s="56"/>
       <c r="AJ24" s="56"/>
@@ -9052,11 +9092,11 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.38636363636364</v>
+        <v>29.356521739130443</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9064,7 +9104,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>1.0240051516275201</v>
+        <v>0.99416325439432285</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9164,7 +9204,9 @@
       <c r="AF25" s="56">
         <v>22.1</v>
       </c>
-      <c r="AG25" s="56"/>
+      <c r="AG25" s="56">
+        <v>20.2</v>
+      </c>
       <c r="AH25" s="56"/>
       <c r="AI25" s="56"/>
       <c r="AJ25" s="56"/>
@@ -9175,11 +9217,11 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>21.940909090909088</v>
+        <v>21.865217391304345</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9187,7 +9229,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>2.0074846347068878</v>
+        <v>1.9317929351021448</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9287,7 +9329,9 @@
       <c r="AF26" s="56">
         <v>12.1</v>
       </c>
-      <c r="AG26" s="56"/>
+      <c r="AG26" s="56">
+        <v>11.5</v>
+      </c>
       <c r="AH26" s="56"/>
       <c r="AI26" s="56"/>
       <c r="AJ26" s="56"/>
@@ -9298,11 +9342,11 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.690909090909088</v>
+        <v>11.682608695652171</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9310,7 +9354,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.3205941907554983</v>
+        <v>1.3122937954985812</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9410,7 +9454,9 @@
       <c r="AF27" s="56">
         <v>27.6</v>
       </c>
-      <c r="AG27" s="56"/>
+      <c r="AG27" s="56">
+        <v>26.2</v>
+      </c>
       <c r="AH27" s="56"/>
       <c r="AI27" s="56"/>
       <c r="AJ27" s="56"/>
@@ -9421,11 +9467,11 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>28.136363636363637</v>
+        <v>28.052173913043479</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9433,7 +9479,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.1476576667677882</v>
+        <v>1.0634679434476304</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9533,7 +9579,9 @@
       <c r="AF28" s="56">
         <v>25.2</v>
       </c>
-      <c r="AG28" s="56"/>
+      <c r="AG28" s="56">
+        <v>26.4</v>
+      </c>
       <c r="AH28" s="56"/>
       <c r="AI28" s="56"/>
       <c r="AJ28" s="56"/>
@@ -9544,11 +9592,11 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>26.563636363636366</v>
+        <v>26.556521739130439</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9556,7 +9604,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>0.81221781215942457</v>
+        <v>0.80510318765349709</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9656,7 +9704,9 @@
       <c r="AF29" s="56">
         <v>28.2</v>
       </c>
-      <c r="AG29" s="56"/>
+      <c r="AG29" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AH29" s="56"/>
       <c r="AI29" s="56"/>
       <c r="AJ29" s="56"/>
@@ -9667,11 +9717,11 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>27.672727272727276</v>
+        <v>27.660869565217393</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9679,7 +9729,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.71868505847003661</v>
+        <v>0.70682735096015392</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9779,7 +9829,9 @@
       <c r="AF30" s="56">
         <v>26.1</v>
       </c>
-      <c r="AG30" s="56"/>
+      <c r="AG30" s="56">
+        <v>24.1</v>
+      </c>
       <c r="AH30" s="56"/>
       <c r="AI30" s="56"/>
       <c r="AJ30" s="56"/>
@@ -9790,11 +9842,11 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>25.204545454545453</v>
+        <v>25.156521739130437</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9802,7 +9854,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.68654397141608214</v>
+        <v>0.63852025600106543</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -9902,7 +9954,9 @@
       <c r="AF31" s="98">
         <v>27.9</v>
       </c>
-      <c r="AG31" s="98"/>
+      <c r="AG31" s="98">
+        <v>28.1</v>
+      </c>
       <c r="AH31" s="98"/>
       <c r="AI31" s="98"/>
       <c r="AJ31" s="98"/>
@@ -9913,11 +9967,11 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>26.86363636363636</v>
+        <v>26.917391304347824</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9925,7 +9979,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.4946877375909615</v>
+        <v>1.5484426783024254</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10025,7 +10079,9 @@
       <c r="AF32" s="56">
         <v>20.666666666666671</v>
       </c>
-      <c r="AG32" s="56"/>
+      <c r="AG32" s="56">
+        <v>19.466666666666669</v>
+      </c>
       <c r="AH32" s="56"/>
       <c r="AI32" s="56"/>
       <c r="AJ32" s="56"/>
@@ -10036,11 +10092,11 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.595454545454547</v>
+        <v>20.546376811594204</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10048,7 +10104,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.9385984933457081</v>
+        <v>2.8895207594853645</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10148,7 +10204,9 @@
       <c r="AF33" s="56">
         <v>28.4</v>
       </c>
-      <c r="AG33" s="56"/>
+      <c r="AG33" s="56">
+        <v>24.95</v>
+      </c>
       <c r="AH33" s="56"/>
       <c r="AI33" s="56"/>
       <c r="AJ33" s="56"/>
@@ -10159,11 +10217,11 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>28.040909090909089</v>
+        <v>27.906521739130437</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10171,7 +10229,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.2134370096965377</v>
+        <v>1.079049657917885</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10271,7 +10329,9 @@
       <c r="AF34" s="56">
         <v>21.466666666666669</v>
       </c>
-      <c r="AG34" s="56"/>
+      <c r="AG34" s="56">
+        <v>20.333333333333329</v>
+      </c>
       <c r="AH34" s="56"/>
       <c r="AI34" s="56"/>
       <c r="AJ34" s="56"/>
@@ -10282,11 +10342,11 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.354545454545459</v>
+        <v>21.310144927536236</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10294,7 +10354,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.5673478628651374</v>
+        <v>1.522947335855914</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10394,7 +10454,9 @@
       <c r="AF35" s="56">
         <v>24.55</v>
       </c>
-      <c r="AG35" s="56"/>
+      <c r="AG35" s="56">
+        <v>22.15</v>
+      </c>
       <c r="AH35" s="56"/>
       <c r="AI35" s="56"/>
       <c r="AJ35" s="56"/>
@@ -10405,11 +10467,11 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.65</v>
+        <v>24.541304347826085</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10417,7 +10479,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.61175210028259741</v>
+        <v>0.50305644810868344</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10517,7 +10579,9 @@
       <c r="AF36" s="56">
         <v>21.05</v>
       </c>
-      <c r="AG36" s="56"/>
+      <c r="AG36" s="56">
+        <v>19.45</v>
+      </c>
       <c r="AH36" s="56"/>
       <c r="AI36" s="56"/>
       <c r="AJ36" s="56"/>
@@ -10528,11 +10592,11 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>20.13636363636364</v>
+        <v>20.106521739130436</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10540,7 +10604,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>1.1375525731452498</v>
+        <v>1.1077106759120454</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10640,7 +10704,9 @@
       <c r="AF37" s="56">
         <v>28.25</v>
       </c>
-      <c r="AG37" s="56"/>
+      <c r="AG37" s="56">
+        <v>25.1</v>
+      </c>
       <c r="AH37" s="56"/>
       <c r="AI37" s="56"/>
       <c r="AJ37" s="56"/>
@@ -10651,11 +10717,11 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>27.49545454545455</v>
+        <v>27.391304347826093</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10663,7 +10729,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.6092246715171683</v>
+        <v>1.5050744738887119</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10756,8 +10822,12 @@
       <c r="AE38" s="56">
         <v>15.85</v>
       </c>
-      <c r="AF38" s="56"/>
-      <c r="AG38" s="56"/>
+      <c r="AF38" s="56">
+        <v>15.55</v>
+      </c>
+      <c r="AG38" s="56">
+        <v>14.9</v>
+      </c>
       <c r="AH38" s="56"/>
       <c r="AI38" s="56"/>
       <c r="AJ38" s="56"/>
@@ -10768,11 +10838,11 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>16.076315789473682</v>
+        <v>15.995238095238093</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10780,7 +10850,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>1.0583867825230016</v>
+        <v>0.97730908828741292</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10878,7 +10948,9 @@
       <c r="AF39" s="56">
         <v>21.8</v>
       </c>
-      <c r="AG39" s="56"/>
+      <c r="AG39" s="56">
+        <v>19.13333333333334</v>
+      </c>
       <c r="AH39" s="56"/>
       <c r="AI39" s="56"/>
       <c r="AJ39" s="56"/>
@@ -10889,11 +10961,11 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>22.526984126984129</v>
+        <v>22.372727272727275</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11112,7 +11184,9 @@
       <c r="AF41" s="56">
         <v>18.8</v>
       </c>
-      <c r="AG41" s="56"/>
+      <c r="AG41" s="56">
+        <v>18.399999999999999</v>
+      </c>
       <c r="AH41" s="56"/>
       <c r="AI41" s="56"/>
       <c r="AJ41" s="56"/>
@@ -11123,11 +11197,11 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>20.36349206349206</v>
+        <v>20.27424242424242</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11135,7 +11209,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>1.8713828721643218</v>
+        <v>1.7821332329146813</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11235,7 +11309,9 @@
       <c r="AF42" s="56">
         <v>28.6</v>
       </c>
-      <c r="AG42" s="56"/>
+      <c r="AG42" s="56">
+        <v>24.7</v>
+      </c>
       <c r="AH42" s="56"/>
       <c r="AI42" s="56"/>
       <c r="AJ42" s="56"/>
@@ -11246,11 +11322,11 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>28.171590909090909</v>
+        <v>28.020652173913046</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11258,7 +11334,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.41890539203263799</v>
+        <v>0.2679666568547745</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11354,7 +11430,9 @@
       <c r="AF43" s="56">
         <v>29.85</v>
       </c>
-      <c r="AG43" s="56"/>
+      <c r="AG43" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AH43" s="56"/>
       <c r="AI43" s="56"/>
       <c r="AJ43" s="56"/>
@@ -11365,11 +11443,11 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>29.557500000000005</v>
+        <v>29.392857142857149</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11477,7 +11555,9 @@
       <c r="AF44" s="56">
         <v>28.425000000000001</v>
       </c>
-      <c r="AG44" s="56"/>
+      <c r="AG44" s="56">
+        <v>25.55</v>
+      </c>
       <c r="AH44" s="56"/>
       <c r="AI44" s="56"/>
       <c r="AJ44" s="56"/>
@@ -11488,11 +11568,11 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.60113636363636</v>
+        <v>28.46847826086956</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11500,7 +11580,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>1.2587929193535388</v>
+        <v>1.1261348165867382</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11600,7 +11680,9 @@
       <c r="AF45" s="56">
         <v>29.65</v>
       </c>
-      <c r="AG45" s="56"/>
+      <c r="AG45" s="56">
+        <v>25.65</v>
+      </c>
       <c r="AH45" s="56"/>
       <c r="AI45" s="56"/>
       <c r="AJ45" s="56"/>
@@ -11611,11 +11693,11 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>29.48863636363637</v>
+        <v>29.321739130434786</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11623,7 +11705,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>1.7205288887049406</v>
+        <v>1.5536316555033558</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11723,7 +11805,9 @@
       <c r="AF46" s="56">
         <v>28.55</v>
       </c>
-      <c r="AG46" s="56"/>
+      <c r="AG46" s="56">
+        <v>27.1</v>
+      </c>
       <c r="AH46" s="56"/>
       <c r="AI46" s="56"/>
       <c r="AJ46" s="56"/>
@@ -11734,11 +11818,11 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v>29.012499999999999</v>
+        <v>28.929347826086957</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11746,7 +11830,7 @@
       </c>
       <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v>1.1063023681025186</v>
+        <v>1.0231501941894763</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11846,7 +11930,9 @@
       <c r="AF47" s="56">
         <v>30.466666666666669</v>
       </c>
-      <c r="AG47" s="56"/>
+      <c r="AG47" s="56">
+        <v>25.933333333333341</v>
+      </c>
       <c r="AH47" s="56"/>
       <c r="AI47" s="56"/>
       <c r="AJ47" s="56"/>
@@ -11857,11 +11943,11 @@
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ47" s="71">
         <f t="shared" si="1"/>
-        <v>30.159090909090914</v>
+        <v>29.975362318840588</v>
       </c>
       <c r="AR47" s="71">
         <f>IFERROR(VLOOKUP(A47,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11869,7 +11955,7 @@
       </c>
       <c r="AS47" s="71">
         <f t="shared" si="2"/>
-        <v>2.1902150497735242</v>
+        <v>2.0064864595231988</v>
       </c>
     </row>
     <row r="48" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12127,7 +12213,9 @@
       <c r="AF50" s="56">
         <v>28.85</v>
       </c>
-      <c r="AG50" s="56"/>
+      <c r="AG50" s="56">
+        <v>25.65</v>
+      </c>
       <c r="AH50" s="56"/>
       <c r="AI50" s="56"/>
       <c r="AJ50" s="56"/>
@@ -12138,11 +12226,11 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>29.488636363636363</v>
+        <v>29.321739130434782</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12150,7 +12238,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>2.1999460176045424</v>
+        <v>2.0330487844029612</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12436,7 +12524,9 @@
       <c r="AF53" s="56">
         <v>28.15</v>
       </c>
-      <c r="AG53" s="56"/>
+      <c r="AG53" s="56">
+        <v>25.5</v>
+      </c>
       <c r="AH53" s="56"/>
       <c r="AI53" s="56"/>
       <c r="AJ53" s="56"/>
@@ -12447,11 +12537,11 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>29.147727272727273</v>
+        <v>28.989130434782609</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12459,7 +12549,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>1.7884809761367251</v>
+        <v>1.629884138192061</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12559,7 +12649,9 @@
       <c r="AF54" s="56">
         <v>31.2</v>
       </c>
-      <c r="AG54" s="56"/>
+      <c r="AG54" s="56">
+        <v>26.15</v>
+      </c>
       <c r="AH54" s="56"/>
       <c r="AI54" s="56"/>
       <c r="AJ54" s="56"/>
@@ -12570,11 +12662,11 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>30.33636363636364</v>
+        <v>30.154347826086958</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12582,7 +12674,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>1.8381376112972205</v>
+        <v>1.6561218010205394</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12668,7 +12760,9 @@
       <c r="AF55" s="56">
         <v>27.65</v>
       </c>
-      <c r="AG55" s="56"/>
+      <c r="AG55" s="56">
+        <v>28</v>
+      </c>
       <c r="AH55" s="56"/>
       <c r="AI55" s="56"/>
       <c r="AJ55" s="56"/>
@@ -12679,11 +12773,11 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ55" s="71">
         <f t="shared" si="1"/>
-        <v>30.626666666666669</v>
+        <v>30.462500000000002</v>
       </c>
       <c r="AR55" s="71">
         <f>IFERROR(VLOOKUP(A55,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12691,7 +12785,7 @@
       </c>
       <c r="AS55" s="71">
         <f t="shared" si="2"/>
-        <v>2.1957069964296281</v>
+        <v>2.0315403297629615</v>
       </c>
     </row>
     <row r="56" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12788,8 +12882,12 @@
       <c r="AE56" s="56">
         <v>28.2</v>
       </c>
-      <c r="AF56" s="56"/>
-      <c r="AG56" s="56"/>
+      <c r="AF56" s="56">
+        <v>27.05</v>
+      </c>
+      <c r="AG56" s="56">
+        <v>27.9</v>
+      </c>
       <c r="AH56" s="56"/>
       <c r="AI56" s="56"/>
       <c r="AJ56" s="56"/>
@@ -12800,11 +12898,11 @@
       <c r="AO56" s="56"/>
       <c r="AP56" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ56" s="71">
         <f t="shared" si="1"/>
-        <v>29.830952380952382</v>
+        <v>29.626086956521739</v>
       </c>
       <c r="AR56" s="71" t="str">
         <f>IFERROR(VLOOKUP(A56,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13308,7 +13406,9 @@
       <c r="AF61" s="56">
         <v>25.6</v>
       </c>
-      <c r="AG61" s="56"/>
+      <c r="AG61" s="56">
+        <v>27.25</v>
+      </c>
       <c r="AH61" s="56"/>
       <c r="AI61" s="56"/>
       <c r="AJ61" s="56"/>
@@ -13319,11 +13419,11 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>26.572727272727278</v>
+        <v>26.602173913043483</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13331,7 +13431,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>0.86605559100131657</v>
+        <v>0.89550223131752205</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13431,7 +13531,9 @@
       <c r="AF62" s="56">
         <v>26.6</v>
       </c>
-      <c r="AG62" s="56"/>
+      <c r="AG62" s="56">
+        <v>25.066666666666659</v>
+      </c>
       <c r="AH62" s="56"/>
       <c r="AI62" s="56"/>
       <c r="AJ62" s="56"/>
@@ -13442,11 +13544,11 @@
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ62" s="71">
         <f t="shared" si="1"/>
-        <v>25.875757575757579</v>
+        <v>25.840579710144929</v>
       </c>
       <c r="AR62" s="71">
         <f>IFERROR(VLOOKUP(A62,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13454,7 +13556,7 @@
       </c>
       <c r="AS62" s="71">
         <f t="shared" si="2"/>
-        <v>1.3367536357936878</v>
+        <v>1.3015757701810386</v>
       </c>
     </row>
     <row r="63" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13691,8 +13793,12 @@
       <c r="AE65" s="56">
         <v>25.55</v>
       </c>
-      <c r="AF65" s="56"/>
-      <c r="AG65" s="56"/>
+      <c r="AF65" s="56">
+        <v>24.05</v>
+      </c>
+      <c r="AG65" s="56">
+        <v>23.85</v>
+      </c>
       <c r="AH65" s="56"/>
       <c r="AI65" s="56"/>
       <c r="AJ65" s="56"/>
@@ -13703,7 +13809,7 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ65" s="71" t="str">
         <f t="shared" si="1"/>
@@ -13815,7 +13921,9 @@
       <c r="AF66" s="56">
         <v>24.4</v>
       </c>
-      <c r="AG66" s="56"/>
+      <c r="AG66" s="56">
+        <v>23.65</v>
+      </c>
       <c r="AH66" s="56"/>
       <c r="AI66" s="56"/>
       <c r="AJ66" s="56"/>
@@ -13826,11 +13934,11 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>25.622727272727271</v>
+        <v>25.536956521739125</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13838,7 +13946,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.71361244244828015</v>
+        <v>0.62784169146013369</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13934,7 +14042,9 @@
       <c r="AF67" s="56">
         <v>25.95</v>
       </c>
-      <c r="AG67" s="56"/>
+      <c r="AG67" s="56">
+        <v>24</v>
+      </c>
       <c r="AH67" s="56"/>
       <c r="AI67" s="56"/>
       <c r="AJ67" s="56"/>
@@ -13945,11 +14055,11 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>25.4</v>
+        <v>25.333333333333332</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13957,7 +14067,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.74879308816878876</v>
+        <v>0.68212642150212233</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14057,7 +14167,9 @@
       <c r="AF68" s="56">
         <v>27.15</v>
       </c>
-      <c r="AG68" s="56"/>
+      <c r="AG68" s="56">
+        <v>26.35</v>
+      </c>
       <c r="AH68" s="56"/>
       <c r="AI68" s="56"/>
       <c r="AJ68" s="56"/>
@@ -14068,11 +14180,11 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>25.411363636363635</v>
+        <v>25.452173913043477</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14080,7 +14192,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>0.88627613362061552</v>
+        <v>0.92708641030045769</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14180,7 +14292,9 @@
       <c r="AF69" s="56">
         <v>23.75</v>
       </c>
-      <c r="AG69" s="56"/>
+      <c r="AG69" s="56">
+        <v>22.7</v>
+      </c>
       <c r="AH69" s="56"/>
       <c r="AI69" s="56"/>
       <c r="AJ69" s="56"/>
@@ -14191,11 +14305,11 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>24.972727272727273</v>
+        <v>24.873913043478261</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14203,7 +14317,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.65032958609526403</v>
+        <v>0.5515153568462523</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14289,7 +14403,9 @@
       <c r="AF70" s="56">
         <v>26.13333333333334</v>
       </c>
-      <c r="AG70" s="56"/>
+      <c r="AG70" s="56">
+        <v>25.966666666666669</v>
+      </c>
       <c r="AH70" s="56"/>
       <c r="AI70" s="56"/>
       <c r="AJ70" s="56"/>
@@ -14300,11 +14416,11 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v>26.451111111111111</v>
+        <v>26.420833333333334</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14312,7 +14428,7 @@
       </c>
       <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v>0.8811524200679095</v>
+        <v>0.85087464229013321</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14412,7 +14528,9 @@
       <c r="AF71" s="56">
         <v>26.233333333333331</v>
       </c>
-      <c r="AG71" s="56"/>
+      <c r="AG71" s="56">
+        <v>24.3</v>
+      </c>
       <c r="AH71" s="56"/>
       <c r="AI71" s="56"/>
       <c r="AJ71" s="56"/>
@@ -14423,11 +14541,11 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>25.975757575757576</v>
+        <v>25.902898550724636</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14435,7 +14553,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.31331466210404813</v>
+        <v>0.24045563707110773</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14533,7 +14651,9 @@
       <c r="AF72" s="56">
         <v>24.93333333333333</v>
       </c>
-      <c r="AG72" s="56"/>
+      <c r="AG72" s="56">
+        <v>25.666666666666671</v>
+      </c>
       <c r="AH72" s="56"/>
       <c r="AI72" s="56"/>
       <c r="AJ72" s="56"/>
@@ -14544,11 +14664,11 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>25.393650793650799</v>
+        <v>25.40606060606061</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14556,7 +14676,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.4204420506912605</v>
+        <v>0.43285186310107093</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14644,7 +14764,9 @@
       <c r="AF73" s="56">
         <v>25.9</v>
       </c>
-      <c r="AG73" s="56"/>
+      <c r="AG73" s="56">
+        <v>24.3</v>
+      </c>
       <c r="AH73" s="56"/>
       <c r="AI73" s="56"/>
       <c r="AJ73" s="56"/>
@@ -14655,11 +14777,11 @@
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ73" s="71">
         <f t="shared" si="4"/>
-        <v>25.824999999999996</v>
+        <v>25.735294117647054</v>
       </c>
       <c r="AR73" s="71" t="str">
         <f>IFERROR(VLOOKUP(A73,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14767,7 +14889,9 @@
       <c r="AF74" s="56">
         <v>22.95</v>
       </c>
-      <c r="AG74" s="56"/>
+      <c r="AG74" s="56">
+        <v>21.15</v>
+      </c>
       <c r="AH74" s="56"/>
       <c r="AI74" s="56"/>
       <c r="AJ74" s="56"/>
@@ -14778,11 +14902,11 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>20.652272727272727</v>
+        <v>20.673913043478262</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14790,7 +14914,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>0.65377397791261771</v>
+        <v>0.67541429411815201</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14890,7 +15014,9 @@
       <c r="AF75" s="56">
         <v>17.733333333333331</v>
       </c>
-      <c r="AG75" s="56"/>
+      <c r="AG75" s="56">
+        <v>18.333333333333329</v>
+      </c>
       <c r="AH75" s="56"/>
       <c r="AI75" s="56"/>
       <c r="AJ75" s="56"/>
@@ -14901,11 +15027,11 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>15.740909090909087</v>
+        <v>15.853623188405791</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14913,7 +15039,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.55986539894229637</v>
+        <v>0.67257949643900083</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15013,7 +15139,9 @@
       <c r="AF76" s="56">
         <v>21.2</v>
       </c>
-      <c r="AG76" s="56"/>
+      <c r="AG76" s="56">
+        <v>19.45</v>
+      </c>
       <c r="AH76" s="56"/>
       <c r="AI76" s="56"/>
       <c r="AJ76" s="56"/>
@@ -15024,11 +15152,11 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>20.787499999999998</v>
+        <v>20.729347826086954</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15036,7 +15164,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>0.98753338847377847</v>
+        <v>0.92938121456073475</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15136,7 +15264,9 @@
       <c r="AF77" s="56">
         <v>25</v>
       </c>
-      <c r="AG77" s="56"/>
+      <c r="AG77" s="56">
+        <v>23.13333333333334</v>
+      </c>
       <c r="AH77" s="56"/>
       <c r="AI77" s="56"/>
       <c r="AJ77" s="56"/>
@@ -15147,11 +15277,11 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>23.924242424242422</v>
+        <v>23.889855072463764</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15159,7 +15289,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.2410015682635027</v>
+        <v>1.2066142164848443</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15259,7 +15389,9 @@
       <c r="AF78" s="56">
         <v>32.349999999999987</v>
       </c>
-      <c r="AG78" s="56"/>
+      <c r="AG78" s="56">
+        <v>29.95</v>
+      </c>
       <c r="AH78" s="56"/>
       <c r="AI78" s="56"/>
       <c r="AJ78" s="56"/>
@@ -15270,11 +15402,11 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v>31.13636363636363</v>
+        <v>31.084782608695651</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15282,7 +15414,7 @@
       </c>
       <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v>1.9524338258409806</v>
+        <v>1.9008527981730019</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15375,7 +15507,9 @@
       <c r="AE79" s="56">
         <v>31.733333333333331</v>
       </c>
-      <c r="AF79" s="56"/>
+      <c r="AF79" s="56">
+        <v>32.066666666666663</v>
+      </c>
       <c r="AG79" s="56"/>
       <c r="AH79" s="56"/>
       <c r="AI79" s="56"/>
@@ -15387,11 +15521,11 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v>31.03859649122807</v>
+        <v>31.089999999999996</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15399,7 +15533,7 @@
       </c>
       <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v>1.5695436067773407</v>
+        <v>1.6209471155492672</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15737,7 +15871,9 @@
       <c r="AF82" s="56">
         <v>27.666666666666671</v>
       </c>
-      <c r="AG82" s="56"/>
+      <c r="AG82" s="56">
+        <v>26.266666666666669</v>
+      </c>
       <c r="AH82" s="56"/>
       <c r="AI82" s="56"/>
       <c r="AJ82" s="56"/>
@@ -15748,11 +15884,11 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ82" s="71">
         <f t="shared" si="4"/>
-        <v>26.034848484848485</v>
+        <v>26.044927536231882</v>
       </c>
       <c r="AR82" s="71">
         <f>IFERROR(VLOOKUP(A82,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15760,7 +15896,7 @@
       </c>
       <c r="AS82" s="71">
         <f t="shared" si="5"/>
-        <v>0.86112602742690569</v>
+        <v>0.87120507881030207</v>
       </c>
     </row>
     <row r="83" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16000,7 +16136,9 @@
       <c r="AF85" s="56">
         <v>30.35</v>
       </c>
-      <c r="AG85" s="56"/>
+      <c r="AG85" s="56">
+        <v>30.5</v>
+      </c>
       <c r="AH85" s="56"/>
       <c r="AI85" s="56"/>
       <c r="AJ85" s="56"/>
@@ -16011,7 +16149,7 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ85" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16123,7 +16261,9 @@
       <c r="AF86" s="56">
         <v>29.9</v>
       </c>
-      <c r="AG86" s="56"/>
+      <c r="AG86" s="56">
+        <v>29.75</v>
+      </c>
       <c r="AH86" s="56"/>
       <c r="AI86" s="56"/>
       <c r="AJ86" s="56"/>
@@ -16134,11 +16274,11 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>29.75454545454545</v>
+        <v>29.754347826086953</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16146,7 +16286,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>1.1424622929906612</v>
+        <v>1.1422646645321635</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16246,7 +16386,9 @@
       <c r="AF87" s="56">
         <v>31.25</v>
       </c>
-      <c r="AG87" s="56"/>
+      <c r="AG87" s="56">
+        <v>27.85</v>
+      </c>
       <c r="AH87" s="56"/>
       <c r="AI87" s="56"/>
       <c r="AJ87" s="56"/>
@@ -16257,11 +16399,11 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>32.1</v>
+        <v>31.915217391304349</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16269,7 +16411,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>3.0938100275376108</v>
+        <v>2.9090274188419585</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16369,7 +16511,9 @@
       <c r="AF88" s="56">
         <v>28.9</v>
       </c>
-      <c r="AG88" s="56"/>
+      <c r="AG88" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AH88" s="56"/>
       <c r="AI88" s="56"/>
       <c r="AJ88" s="56"/>
@@ -16380,11 +16524,11 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>30.275000000000002</v>
+        <v>30.158695652173918</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16392,7 +16536,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>1.5841253840245919</v>
+        <v>1.467821036198508</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16597,7 +16741,9 @@
       <c r="AD90" s="56"/>
       <c r="AE90" s="56"/>
       <c r="AF90" s="56"/>
-      <c r="AG90" s="56"/>
+      <c r="AG90" s="56">
+        <v>29.75</v>
+      </c>
       <c r="AH90" s="56"/>
       <c r="AI90" s="56"/>
       <c r="AJ90" s="56"/>
@@ -16608,11 +16754,11 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v>32.336111111111109</v>
+        <v>32.199999999999996</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16620,7 +16766,7 @@
       </c>
       <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v>3.3010510531984494</v>
+        <v>3.1649399420873365</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16835,7 +16981,9 @@
       <c r="AF92" s="56">
         <v>17.600000000000001</v>
       </c>
-      <c r="AG92" s="56"/>
+      <c r="AG92" s="56">
+        <v>16.850000000000001</v>
+      </c>
       <c r="AH92" s="56"/>
       <c r="AI92" s="56"/>
       <c r="AJ92" s="56"/>
@@ -16846,11 +16994,11 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>17.624242424242428</v>
+        <v>17.590579710144933</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16858,7 +17006,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>1.4608983382209573</v>
+        <v>1.4272356241234618</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16958,7 +17106,9 @@
       <c r="AF93" s="56">
         <v>23.266666666666669</v>
       </c>
-      <c r="AG93" s="56"/>
+      <c r="AG93" s="56">
+        <v>23.533333333333331</v>
+      </c>
       <c r="AH93" s="56"/>
       <c r="AI93" s="56"/>
       <c r="AJ93" s="56"/>
@@ -16969,11 +17119,11 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>23.630303030303029</v>
+        <v>23.626086956521739</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16981,7 +17131,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.520815164433408</v>
+        <v>1.5165990906521181</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17081,7 +17231,9 @@
       <c r="AF94" s="56">
         <v>18.149999999999999</v>
       </c>
-      <c r="AG94" s="56"/>
+      <c r="AG94" s="56">
+        <v>16.8</v>
+      </c>
       <c r="AH94" s="56"/>
       <c r="AI94" s="56"/>
       <c r="AJ94" s="56"/>
@@ -17092,11 +17244,11 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.364772727272729</v>
+        <v>17.34021739130435</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17104,7 +17256,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.2695455813381606</v>
+        <v>1.244990245369781</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17204,7 +17356,9 @@
       <c r="AF95" s="56">
         <v>15.5</v>
       </c>
-      <c r="AG95" s="56"/>
+      <c r="AG95" s="56">
+        <v>13.55</v>
+      </c>
       <c r="AH95" s="56"/>
       <c r="AI95" s="56"/>
       <c r="AJ95" s="56"/>
@@ -17215,11 +17369,11 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>14.711363636363638</v>
+        <v>14.660869565217393</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17227,7 +17381,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>1.0785555002117775</v>
+        <v>1.0280614290655326</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17485,7 +17639,9 @@
       <c r="AF98" s="56">
         <v>12.65</v>
       </c>
-      <c r="AG98" s="56"/>
+      <c r="AG98" s="56">
+        <v>13.65</v>
+      </c>
       <c r="AH98" s="56"/>
       <c r="AI98" s="56"/>
       <c r="AJ98" s="56"/>
@@ -17496,11 +17652,11 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>13.211363636363638</v>
+        <v>13.230434782608697</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17604,7 +17760,9 @@
       <c r="AF99" s="56">
         <v>14.266666666666669</v>
       </c>
-      <c r="AG99" s="56"/>
+      <c r="AG99" s="56">
+        <v>13.96666666666667</v>
+      </c>
       <c r="AH99" s="56"/>
       <c r="AI99" s="56"/>
       <c r="AJ99" s="56"/>
@@ -17615,11 +17773,11 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ99" s="71">
         <f t="shared" si="4"/>
-        <v>14.453333333333333</v>
+        <v>14.430158730158732</v>
       </c>
       <c r="AR99" s="71" t="str">
         <f>IFERROR(VLOOKUP(A99,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17717,7 +17875,9 @@
       <c r="AF100" s="56">
         <v>16.2</v>
       </c>
-      <c r="AG100" s="56"/>
+      <c r="AG100" s="56">
+        <v>15.66666666666667</v>
+      </c>
       <c r="AH100" s="56"/>
       <c r="AI100" s="56"/>
       <c r="AJ100" s="56"/>
@@ -17728,11 +17888,11 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ100" s="71">
         <f t="shared" si="4"/>
-        <v>16.333333333333336</v>
+        <v>16.296296296296298</v>
       </c>
       <c r="AR100" s="71">
         <f>IFERROR(VLOOKUP(A100,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17740,7 +17900,7 @@
       </c>
       <c r="AS100" s="71">
         <f t="shared" si="5"/>
-        <v>2.023975427225345</v>
+        <v>1.9869383901883069</v>
       </c>
     </row>
     <row r="101" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17830,7 +17990,9 @@
       <c r="AF101" s="56">
         <v>14.05</v>
       </c>
-      <c r="AG101" s="56"/>
+      <c r="AG101" s="56">
+        <v>12.4</v>
+      </c>
       <c r="AH101" s="56"/>
       <c r="AI101" s="56"/>
       <c r="AJ101" s="56"/>
@@ -17841,11 +18003,11 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ101" s="71">
         <f t="shared" si="4"/>
-        <v>13.552941176470588</v>
+        <v>13.488888888888889</v>
       </c>
       <c r="AR101" s="71">
         <f>IFERROR(VLOOKUP(A101,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17853,7 +18015,7 @@
       </c>
       <c r="AS101" s="71">
         <f t="shared" si="5"/>
-        <v>1.2205375138592984</v>
+        <v>1.1564852262775993</v>
       </c>
     </row>
     <row r="102" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17947,7 +18109,9 @@
       <c r="AF102" s="56">
         <v>14.2</v>
       </c>
-      <c r="AG102" s="56"/>
+      <c r="AG102" s="56">
+        <v>13.06666666666667</v>
+      </c>
       <c r="AH102" s="56"/>
       <c r="AI102" s="56"/>
       <c r="AJ102" s="56"/>
@@ -17958,11 +18122,11 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ102" s="71">
         <f t="shared" si="4"/>
-        <v>13.108771929824563</v>
+        <v>13.106666666666669</v>
       </c>
       <c r="AR102" s="71">
         <f>IFERROR(VLOOKUP(A102,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17970,7 +18134,7 @@
       </c>
       <c r="AS102" s="71">
         <f t="shared" si="5"/>
-        <v>1.8617765604386722</v>
+        <v>1.8596712972807783</v>
       </c>
     </row>
     <row r="103" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18222,7 +18386,9 @@
       <c r="AF105" s="56">
         <v>18</v>
       </c>
-      <c r="AG105" s="56"/>
+      <c r="AG105" s="56">
+        <v>19.466666666666669</v>
+      </c>
       <c r="AH105" s="56"/>
       <c r="AI105" s="56"/>
       <c r="AJ105" s="56"/>
@@ -18233,11 +18399,11 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>18.05964912280702</v>
+        <v>18.130000000000003</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18245,7 +18411,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>1.015111614330749</v>
+        <v>1.0854624915237316</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18406,7 +18572,9 @@
       <c r="AF107" s="56">
         <v>14.8</v>
       </c>
-      <c r="AG107" s="56"/>
+      <c r="AG107" s="56">
+        <v>15.266666666666669</v>
+      </c>
       <c r="AH107" s="56"/>
       <c r="AI107" s="56"/>
       <c r="AJ107" s="56"/>
@@ -18417,7 +18585,7 @@
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ107" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18529,7 +18697,9 @@
       <c r="AF108" s="56">
         <v>15.5</v>
       </c>
-      <c r="AG108" s="56"/>
+      <c r="AG108" s="56">
+        <v>14.85</v>
+      </c>
       <c r="AH108" s="56"/>
       <c r="AI108" s="56"/>
       <c r="AJ108" s="56"/>
@@ -18540,11 +18710,11 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>14.063636363636364</v>
+        <v>14.097826086956525</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18552,7 +18722,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>-0.16539655109544604</v>
+        <v>-0.13120682777528536</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18652,7 +18822,9 @@
       <c r="AF109" s="56">
         <v>14.9</v>
       </c>
-      <c r="AG109" s="56"/>
+      <c r="AG109" s="56">
+        <v>13.85</v>
+      </c>
       <c r="AH109" s="56"/>
       <c r="AI109" s="56"/>
       <c r="AJ109" s="56"/>
@@ -18663,11 +18835,11 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>14.540909090909087</v>
+        <v>14.510869565217389</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18675,7 +18847,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.82714600340129785</v>
+        <v>0.7971064777095993</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18775,7 +18947,9 @@
       <c r="AF110" s="56">
         <v>17.86666666666666</v>
       </c>
-      <c r="AG110" s="56"/>
+      <c r="AG110" s="56">
+        <v>16.266666666666669</v>
+      </c>
       <c r="AH110" s="56"/>
       <c r="AI110" s="56"/>
       <c r="AJ110" s="56"/>
@@ -18786,11 +18960,11 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.515151515151508</v>
+        <v>17.460869565217386</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18798,7 +18972,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.58018947668461962</v>
+        <v>0.52590752675049757</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18898,7 +19072,9 @@
       <c r="AF111" s="56">
         <v>16.56666666666667</v>
       </c>
-      <c r="AG111" s="56"/>
+      <c r="AG111" s="56">
+        <v>14.93333333333333</v>
+      </c>
       <c r="AH111" s="56"/>
       <c r="AI111" s="56"/>
       <c r="AJ111" s="56"/>
@@ -18909,11 +19085,11 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>15.96818181818182</v>
+        <v>15.923188405797104</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18921,7 +19097,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.46581829460863133</v>
+        <v>0.4208248822239149</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19021,7 +19197,9 @@
       <c r="AF112" s="56">
         <v>18.333333333333329</v>
       </c>
-      <c r="AG112" s="56"/>
+      <c r="AG112" s="56">
+        <v>16.533333333333331</v>
+      </c>
       <c r="AH112" s="56"/>
       <c r="AI112" s="56"/>
       <c r="AJ112" s="56"/>
@@ -19032,11 +19210,11 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>17.848484848484844</v>
+        <v>17.791304347826085</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19044,7 +19222,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.4687885873827646</v>
+        <v>1.4116080867240051</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19142,7 +19320,9 @@
       <c r="AF113" s="56">
         <v>19.8</v>
       </c>
-      <c r="AG113" s="56"/>
+      <c r="AG113" s="56">
+        <v>16.8</v>
+      </c>
       <c r="AH113" s="56"/>
       <c r="AI113" s="56"/>
       <c r="AJ113" s="56"/>
@@ -19153,11 +19333,11 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v>19.149206349206349</v>
+        <v>19.042424242424243</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19165,7 +19345,7 @@
       </c>
       <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v>1.0248188816498178</v>
+        <v>0.91803677486771207</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19356,7 +19536,9 @@
       <c r="AF115" s="56">
         <v>26.1</v>
       </c>
-      <c r="AG115" s="56"/>
+      <c r="AG115" s="56">
+        <v>23.15</v>
+      </c>
       <c r="AH115" s="56"/>
       <c r="AI115" s="56"/>
       <c r="AJ115" s="56"/>
@@ -19367,11 +19549,11 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>26.27840909090909</v>
+        <v>26.142391304347825</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19379,7 +19561,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.43392911315606852</v>
+        <v>0.29791132659480368</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19479,7 +19661,9 @@
       <c r="AF116" s="56">
         <v>19.93333333333333</v>
       </c>
-      <c r="AG116" s="56"/>
+      <c r="AG116" s="56">
+        <v>18.666666666666671</v>
+      </c>
       <c r="AH116" s="56"/>
       <c r="AI116" s="56"/>
       <c r="AJ116" s="56"/>
@@ -19490,11 +19674,11 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>19.23030303030303</v>
+        <v>19.205797101449274</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19502,7 +19686,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>0.83379786396221078</v>
+        <v>0.80929193510845465</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19602,7 +19786,9 @@
       <c r="AF117" s="56">
         <v>26.466666666666669</v>
       </c>
-      <c r="AG117" s="56"/>
+      <c r="AG117" s="56">
+        <v>24.2</v>
+      </c>
       <c r="AH117" s="56"/>
       <c r="AI117" s="56"/>
       <c r="AJ117" s="56"/>
@@ -19613,11 +19799,11 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>26.333333333333339</v>
+        <v>26.240579710144935</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19625,7 +19811,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>0.96449372759859031</v>
+        <v>0.87174010441018623</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19722,8 +19908,12 @@
       <c r="AE118" s="56">
         <v>29.2</v>
       </c>
-      <c r="AF118" s="56"/>
-      <c r="AG118" s="56"/>
+      <c r="AF118" s="56">
+        <v>29.333333333333329</v>
+      </c>
+      <c r="AG118" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AH118" s="56"/>
       <c r="AI118" s="56"/>
       <c r="AJ118" s="56"/>
@@ -19734,11 +19924,11 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ118" s="71">
         <f t="shared" si="4"/>
-        <v>28.615873015873017</v>
+        <v>28.594202898550726</v>
       </c>
       <c r="AR118" s="71">
         <f>IFERROR(VLOOKUP(A118,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19746,7 +19936,7 @@
       </c>
       <c r="AS118" s="71">
         <f t="shared" si="5"/>
-        <v>2.8625934459805578</v>
+        <v>2.8409233286582669</v>
       </c>
     </row>
     <row r="119" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19846,7 +20036,9 @@
       <c r="AF119" s="56">
         <v>24.4</v>
       </c>
-      <c r="AG119" s="56"/>
+      <c r="AG119" s="56">
+        <v>24.066666666666659</v>
+      </c>
       <c r="AH119" s="56"/>
       <c r="AI119" s="56"/>
       <c r="AJ119" s="56"/>
@@ -19857,11 +20049,11 @@
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ119" s="71">
         <f t="shared" si="4"/>
-        <v>23.54545454545455</v>
+        <v>23.568115942028989</v>
       </c>
       <c r="AR119" s="71">
         <f>IFERROR(VLOOKUP(A119,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19869,7 +20061,7 @@
       </c>
       <c r="AS119" s="71">
         <f t="shared" si="5"/>
-        <v>1.8170136852395409</v>
+        <v>1.8396750818139793</v>
       </c>
     </row>
     <row r="120" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20149,7 +20341,9 @@
       <c r="AF122" s="56">
         <v>12.866666666666671</v>
       </c>
-      <c r="AG122" s="56"/>
+      <c r="AG122" s="56">
+        <v>12.2</v>
+      </c>
       <c r="AH122" s="56"/>
       <c r="AI122" s="56"/>
       <c r="AJ122" s="56"/>
@@ -20160,11 +20354,11 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>12.231818181818181</v>
+        <v>12.230434782608693</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20172,7 +20366,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>1.9290611858479014</v>
+        <v>1.927677786638414</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20349,7 +20543,9 @@
       <c r="AF124" s="56">
         <v>16.8</v>
       </c>
-      <c r="AG124" s="56"/>
+      <c r="AG124" s="56">
+        <v>14.8</v>
+      </c>
       <c r="AH124" s="56"/>
       <c r="AI124" s="56"/>
       <c r="AJ124" s="56"/>
@@ -20360,11 +20556,11 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ124" s="71">
         <f t="shared" si="4"/>
-        <v>15.942857142857143</v>
+        <v>15.890909090909092</v>
       </c>
       <c r="AR124" s="71">
         <f>IFERROR(VLOOKUP(A124,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20372,7 +20568,7 @@
       </c>
       <c r="AS124" s="71">
         <f t="shared" si="5"/>
-        <v>0.89379818331363303</v>
+        <v>0.8418501313655824</v>
       </c>
     </row>
     <row r="125" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20537,7 +20733,9 @@
       <c r="AF126" s="56">
         <v>12.2</v>
       </c>
-      <c r="AG126" s="56"/>
+      <c r="AG126" s="56">
+        <v>11.06666666666667</v>
+      </c>
       <c r="AH126" s="56"/>
       <c r="AI126" s="56"/>
       <c r="AJ126" s="56"/>
@@ -20548,11 +20746,11 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ126" s="71">
         <f t="shared" si="4"/>
-        <v>12.079999999999997</v>
+        <v>12.016666666666664</v>
       </c>
       <c r="AR126" s="71">
         <f>IFERROR(VLOOKUP(A126,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20560,7 +20758,7 @@
       </c>
       <c r="AS126" s="71">
         <f t="shared" si="5"/>
-        <v>1.3675537839362573</v>
+        <v>1.3042204506029247</v>
       </c>
     </row>
     <row r="127" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20897,7 +21095,9 @@
       <c r="AF130" s="56">
         <v>16.7</v>
       </c>
-      <c r="AG130" s="56"/>
+      <c r="AG130" s="56">
+        <v>15.8</v>
+      </c>
       <c r="AH130" s="56"/>
       <c r="AI130" s="56"/>
       <c r="AJ130" s="56"/>
@@ -20908,11 +21108,11 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ130" s="71">
         <f t="shared" si="4"/>
-        <v>15.910606060606062</v>
+        <v>15.905797101449277</v>
       </c>
       <c r="AR130" s="71">
         <f>IFERROR(VLOOKUP(A130,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20920,7 +21120,7 @@
       </c>
       <c r="AS130" s="71">
         <f t="shared" si="5"/>
-        <v>1.6573636861386127</v>
+        <v>1.6525547269818279</v>
       </c>
     </row>
     <row r="131" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21020,7 +21220,9 @@
       <c r="AF131" s="56">
         <v>18.350000000000001</v>
       </c>
-      <c r="AG131" s="56"/>
+      <c r="AG131" s="56">
+        <v>18.55</v>
+      </c>
       <c r="AH131" s="56"/>
       <c r="AI131" s="56"/>
       <c r="AJ131" s="56"/>
@@ -21031,11 +21233,11 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>18.325000000000003</v>
+        <v>18.334782608695654</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21043,7 +21245,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.5321030010960541</v>
+        <v>1.5418856097917057</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21222,7 +21424,9 @@
       <c r="AF133" s="56">
         <v>14</v>
       </c>
-      <c r="AG133" s="56"/>
+      <c r="AG133" s="56">
+        <v>13.03333333333333</v>
+      </c>
       <c r="AH133" s="56"/>
       <c r="AI133" s="56"/>
       <c r="AJ133" s="56"/>
@@ -21233,11 +21437,11 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>14.037878787878787</v>
+        <v>13.994202898550723</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21245,7 +21449,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>1.4025390132249473</v>
+        <v>1.3588631238968834</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21342,8 +21546,12 @@
       <c r="AE134" s="56">
         <v>18.13333333333334</v>
       </c>
-      <c r="AF134" s="56"/>
-      <c r="AG134" s="56"/>
+      <c r="AF134" s="56">
+        <v>18.2</v>
+      </c>
+      <c r="AG134" s="56">
+        <v>17.866666666666671</v>
+      </c>
       <c r="AH134" s="56"/>
       <c r="AI134" s="56"/>
       <c r="AJ134" s="56"/>
@@ -21354,11 +21562,11 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>17.952380952380949</v>
+        <v>17.959420289855071</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21366,7 +21574,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>2.3702021099972796</v>
+        <v>2.3772414474714019</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21466,7 +21674,9 @@
       <c r="AF135" s="56">
         <v>19.2</v>
       </c>
-      <c r="AG135" s="56"/>
+      <c r="AG135" s="56">
+        <v>19.399999999999999</v>
+      </c>
       <c r="AH135" s="56"/>
       <c r="AI135" s="56"/>
       <c r="AJ135" s="56"/>
@@ -21477,11 +21687,11 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>20.754545454545454</v>
+        <v>20.695652173913043</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21489,7 +21699,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>2.0726648171403248</v>
+        <v>2.0137715365079139</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21586,8 +21796,12 @@
       <c r="AE136" s="56">
         <v>11.866666666666671</v>
       </c>
-      <c r="AF136" s="56"/>
-      <c r="AG136" s="56"/>
+      <c r="AF136" s="56">
+        <v>11.733333333333331</v>
+      </c>
+      <c r="AG136" s="56">
+        <v>11.4</v>
+      </c>
       <c r="AH136" s="56"/>
       <c r="AI136" s="56"/>
       <c r="AJ136" s="56"/>
@@ -21598,11 +21812,11 @@
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ136" s="71">
         <f t="shared" si="7"/>
-        <v>11.187301587301587</v>
+        <v>11.220289855072462</v>
       </c>
       <c r="AR136" s="71">
         <f>IFERROR(VLOOKUP(A136,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21610,7 +21824,7 @@
       </c>
       <c r="AS136" s="71">
         <f t="shared" si="8"/>
-        <v>0.32965151314512653</v>
+        <v>0.3626397809160018</v>
       </c>
     </row>
     <row r="137" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21789,7 +22003,9 @@
       <c r="AF138" s="56">
         <v>22.666666666666671</v>
       </c>
-      <c r="AG138" s="56"/>
+      <c r="AG138" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="AH138" s="56"/>
       <c r="AI138" s="56"/>
       <c r="AJ138" s="56"/>
@@ -21800,11 +22016,11 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>22.324242424242428</v>
+        <v>22.281159420289857</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21812,7 +22028,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>2.3140213268940286</v>
+        <v>2.2709383229414577</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21912,7 +22128,9 @@
       <c r="AF139" s="56">
         <v>14.15</v>
       </c>
-      <c r="AG139" s="56"/>
+      <c r="AG139" s="56">
+        <v>13.75</v>
+      </c>
       <c r="AH139" s="56"/>
       <c r="AI139" s="56"/>
       <c r="AJ139" s="56"/>
@@ -21923,11 +22141,11 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>14.079545454545451</v>
+        <v>14.065217391304346</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21935,7 +22153,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.1753276817114422</v>
+        <v>1.1609996184703366</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22035,7 +22253,9 @@
       <c r="AF140" s="56">
         <v>15.95</v>
       </c>
-      <c r="AG140" s="56"/>
+      <c r="AG140" s="56">
+        <v>16.100000000000001</v>
+      </c>
       <c r="AH140" s="56"/>
       <c r="AI140" s="56"/>
       <c r="AJ140" s="56"/>
@@ -22046,11 +22266,11 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.529545454545453</v>
+        <v>16.510869565217391</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22058,7 +22278,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.93519488277553187</v>
+        <v>0.91651899344747001</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22158,7 +22378,9 @@
       <c r="AF141" s="56">
         <v>13.866666666666671</v>
       </c>
-      <c r="AG141" s="56"/>
+      <c r="AG141" s="56">
+        <v>12.93333333333333</v>
+      </c>
       <c r="AH141" s="56"/>
       <c r="AI141" s="56"/>
       <c r="AJ141" s="56"/>
@@ -22169,11 +22391,11 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>13.609090909090911</v>
+        <v>13.579710144927537</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22181,7 +22403,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.5950615122528617</v>
+        <v>1.5656807480894877</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22276,8 +22498,12 @@
       <c r="AE142" s="56">
         <v>12.2</v>
       </c>
-      <c r="AF142" s="56"/>
-      <c r="AG142" s="56"/>
+      <c r="AF142" s="56">
+        <v>11.75</v>
+      </c>
+      <c r="AG142" s="56">
+        <v>11.725</v>
+      </c>
       <c r="AH142" s="56"/>
       <c r="AI142" s="56"/>
       <c r="AJ142" s="56"/>
@@ -22288,11 +22514,11 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>11.6975</v>
+        <v>11.701136363636364</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22300,7 +22526,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>1.168514023518199</v>
+        <v>1.1721503871545629</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22400,7 +22626,9 @@
       <c r="AF143" s="56">
         <v>26.8</v>
       </c>
-      <c r="AG143" s="56"/>
+      <c r="AG143" s="56">
+        <v>26.6</v>
+      </c>
       <c r="AH143" s="56"/>
       <c r="AI143" s="56"/>
       <c r="AJ143" s="56"/>
@@ -22411,11 +22639,11 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>27.681818181818176</v>
+        <v>27.634782608695648</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22423,7 +22651,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>1.8198780896522955</v>
+        <v>1.7728425165297672</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22523,7 +22751,9 @@
       <c r="AF144" s="56">
         <v>16.266666666666669</v>
       </c>
-      <c r="AG144" s="56"/>
+      <c r="AG144" s="56">
+        <v>15</v>
+      </c>
       <c r="AH144" s="56"/>
       <c r="AI144" s="56"/>
       <c r="AJ144" s="56"/>
@@ -22534,11 +22764,11 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ144" s="71">
         <f t="shared" si="7"/>
-        <v>15.624242424242425</v>
+        <v>15.597101449275362</v>
       </c>
       <c r="AR144" s="71">
         <f>IFERROR(VLOOKUP(A144,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22546,7 +22776,7 @@
       </c>
       <c r="AS144" s="71">
         <f t="shared" si="8"/>
-        <v>-8.8643329671864279E-2</v>
+        <v>-0.11578430463892708</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22646,7 +22876,9 @@
       <c r="AF145" s="56">
         <v>20.8</v>
       </c>
-      <c r="AG145" s="56"/>
+      <c r="AG145" s="56">
+        <v>19.13333333333334</v>
+      </c>
       <c r="AH145" s="56"/>
       <c r="AI145" s="56"/>
       <c r="AJ145" s="56"/>
@@ -22657,11 +22889,11 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>19.457575757575757</v>
+        <v>19.443478260869565</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22669,7 +22901,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>0.41555922307763637</v>
+        <v>0.40146172637144417</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22766,8 +22998,12 @@
       <c r="AE146" s="56">
         <v>29.13333333333334</v>
       </c>
-      <c r="AF146" s="56"/>
-      <c r="AG146" s="56"/>
+      <c r="AF146" s="56">
+        <v>31.466666666666669</v>
+      </c>
+      <c r="AG146" s="56">
+        <v>29.13333333333334</v>
+      </c>
       <c r="AH146" s="56"/>
       <c r="AI146" s="56"/>
       <c r="AJ146" s="56"/>
@@ -22778,11 +23014,11 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ146" s="71">
         <f t="shared" si="7"/>
-        <v>29.850793650793644</v>
+        <v>29.889855072463764</v>
       </c>
       <c r="AR146" s="71">
         <f>IFERROR(VLOOKUP(A146,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22790,7 +23026,7 @@
       </c>
       <c r="AS146" s="71">
         <f t="shared" si="8"/>
-        <v>1.0935941129964135</v>
+        <v>1.132655534666533</v>
       </c>
     </row>
     <row r="147" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22890,7 +23126,9 @@
       <c r="AF147" s="56">
         <v>26.666666666666671</v>
       </c>
-      <c r="AG147" s="56"/>
+      <c r="AG147" s="56">
+        <v>24.466666666666669</v>
+      </c>
       <c r="AH147" s="56"/>
       <c r="AI147" s="56"/>
       <c r="AJ147" s="56"/>
@@ -22901,11 +23139,11 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>25.151515151515152</v>
+        <v>25.121739130434786</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22913,7 +23151,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>1.647457659651792</v>
+        <v>1.6176816385714261</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23009,7 +23247,9 @@
       <c r="AF148" s="56">
         <v>30</v>
       </c>
-      <c r="AG148" s="56"/>
+      <c r="AG148" s="56">
+        <v>28.666666666666671</v>
+      </c>
       <c r="AH148" s="56"/>
       <c r="AI148" s="56"/>
       <c r="AJ148" s="56"/>
@@ -23020,11 +23260,11 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>30.373333333333335</v>
+        <v>30.292063492063491</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23032,7 +23272,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.7318021024785537</v>
+        <v>1.6505322612087099</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23132,7 +23372,9 @@
       <c r="AF149" s="56">
         <v>23.13333333333334</v>
       </c>
-      <c r="AG149" s="56"/>
+      <c r="AG149" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="AH149" s="56"/>
       <c r="AI149" s="56"/>
       <c r="AJ149" s="56"/>
@@ -23143,11 +23385,11 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v>23.663636363636364</v>
+        <v>23.562318840579714</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23155,7 +23397,7 @@
       </c>
       <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v>1.787568590683513</v>
+        <v>1.6862510676268627</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23334,7 +23576,9 @@
       <c r="AF151" s="56">
         <v>23.2</v>
       </c>
-      <c r="AG151" s="56"/>
+      <c r="AG151" s="56">
+        <v>20</v>
+      </c>
       <c r="AH151" s="56"/>
       <c r="AI151" s="56"/>
       <c r="AJ151" s="56"/>
@@ -23345,11 +23589,11 @@
       <c r="AO151" s="56"/>
       <c r="AP151" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ151" s="71">
         <f t="shared" si="7"/>
-        <v>23.428787878787876</v>
+        <v>23.279710144927535</v>
       </c>
       <c r="AR151" s="71">
         <f>IFERROR(VLOOKUP(A151,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23357,7 +23601,7 @@
       </c>
       <c r="AS151" s="71">
         <f t="shared" si="8"/>
-        <v>1.616200600167236</v>
+        <v>1.4671228663068945</v>
       </c>
     </row>
     <row r="152" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23615,7 +23859,9 @@
       <c r="AF154" s="56">
         <v>20</v>
       </c>
-      <c r="AG154" s="56"/>
+      <c r="AG154" s="56">
+        <v>19.899999999999999</v>
+      </c>
       <c r="AH154" s="56"/>
       <c r="AI154" s="56"/>
       <c r="AJ154" s="56"/>
@@ -23626,11 +23872,11 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ154" s="71">
         <f t="shared" si="7"/>
-        <v>20.536363636363639</v>
+        <v>20.508695652173916</v>
       </c>
       <c r="AR154" s="71">
         <f>IFERROR(VLOOKUP(A154,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23638,7 +23884,7 @@
       </c>
       <c r="AS154" s="71">
         <f t="shared" si="8"/>
-        <v>1.0227428819686999</v>
+        <v>0.99507489777897717</v>
       </c>
     </row>
     <row r="155" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23738,7 +23984,9 @@
       <c r="AF155" s="56">
         <v>28.466666666666669</v>
       </c>
-      <c r="AG155" s="56"/>
+      <c r="AG155" s="56">
+        <v>27.666666666666671</v>
+      </c>
       <c r="AH155" s="56"/>
       <c r="AI155" s="56"/>
       <c r="AJ155" s="56"/>
@@ -23749,11 +23997,11 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>29.054545454545458</v>
+        <v>28.994202898550725</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23761,7 +24009,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>1.3317588936896598</v>
+        <v>1.2714163376949266</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23932,7 +24180,9 @@
       <c r="AF157" s="56">
         <v>29.2</v>
       </c>
-      <c r="AG157" s="56"/>
+      <c r="AG157" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AH157" s="56"/>
       <c r="AI157" s="56"/>
       <c r="AJ157" s="56"/>
@@ -23943,11 +24193,11 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ157" s="71">
         <f t="shared" si="7"/>
-        <v>29.529629629629635</v>
+        <v>29.428070175438602</v>
       </c>
       <c r="AR157" s="71">
         <f>IFERROR(VLOOKUP(A157,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23955,7 +24205,7 @@
       </c>
       <c r="AS157" s="71">
         <f t="shared" si="8"/>
-        <v>1.9452021330202349</v>
+        <v>1.8436426788292017</v>
       </c>
     </row>
     <row r="158" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24049,7 +24299,9 @@
         <v>28.06666666666667</v>
       </c>
       <c r="AF158" s="56"/>
-      <c r="AG158" s="56"/>
+      <c r="AG158" s="56">
+        <v>26.933333333333341</v>
+      </c>
       <c r="AH158" s="56"/>
       <c r="AI158" s="56"/>
       <c r="AJ158" s="56"/>
@@ -24060,11 +24312,11 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>30.221052631578949</v>
+        <v>30.056666666666672</v>
       </c>
       <c r="AR158" s="71">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24072,7 +24324,7 @@
       </c>
       <c r="AS158" s="71">
         <f t="shared" si="8"/>
-        <v>2.2026404644987494</v>
+        <v>2.038254499586472</v>
       </c>
     </row>
     <row r="159" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24166,7 +24418,9 @@
       <c r="AF159" s="56">
         <v>20.2</v>
       </c>
-      <c r="AG159" s="56"/>
+      <c r="AG159" s="56">
+        <v>19.266666666666669</v>
+      </c>
       <c r="AH159" s="56"/>
       <c r="AI159" s="56"/>
       <c r="AJ159" s="56"/>
@@ -24177,11 +24431,11 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>20.449122807017545</v>
+        <v>20.39</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24189,7 +24443,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>1.4581856923271452</v>
+        <v>1.3990628853096005</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24289,7 +24543,9 @@
       <c r="AF160" s="56">
         <v>27.266666666666669</v>
       </c>
-      <c r="AG160" s="56"/>
+      <c r="AG160" s="56">
+        <v>25.6</v>
+      </c>
       <c r="AH160" s="56"/>
       <c r="AI160" s="56"/>
       <c r="AJ160" s="56"/>
@@ -24300,11 +24556,11 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>27.081818181818189</v>
+        <v>27.017391304347836</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24388,9 +24644,13 @@
         <v>17.666666666666671</v>
       </c>
       <c r="AD161" s="56"/>
-      <c r="AE161" s="56"/>
+      <c r="AE161" s="56">
+        <v>18.8</v>
+      </c>
       <c r="AF161" s="56"/>
-      <c r="AG161" s="56"/>
+      <c r="AG161" s="56">
+        <v>19.06666666666667</v>
+      </c>
       <c r="AH161" s="56"/>
       <c r="AI161" s="56"/>
       <c r="AJ161" s="56"/>
@@ -24401,7 +24661,7 @@
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ161" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24513,7 +24773,9 @@
       <c r="AF162" s="56">
         <v>28.933333333333341</v>
       </c>
-      <c r="AG162" s="56"/>
+      <c r="AG162" s="56">
+        <v>27</v>
+      </c>
       <c r="AH162" s="56"/>
       <c r="AI162" s="56"/>
       <c r="AJ162" s="56"/>
@@ -24524,11 +24786,11 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>29.024242424242434</v>
+        <v>28.936231884057978</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24536,7 +24798,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>0.45070503636815573</v>
+        <v>0.36269449618369975</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24636,7 +24898,9 @@
       <c r="AF163" s="56">
         <v>21.266666666666669</v>
       </c>
-      <c r="AG163" s="56"/>
+      <c r="AG163" s="56">
+        <v>21.06666666666667</v>
+      </c>
       <c r="AH163" s="56"/>
       <c r="AI163" s="56"/>
       <c r="AJ163" s="56"/>
@@ -24647,11 +24911,11 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.448484848484846</v>
+        <v>21.431884057971011</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24659,7 +24923,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>0.19906103288426635</v>
+        <v>0.18246024237043201</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24759,7 +25023,9 @@
       <c r="AF164" s="56">
         <v>26</v>
       </c>
-      <c r="AG164" s="56"/>
+      <c r="AG164" s="56">
+        <v>25.15</v>
+      </c>
       <c r="AH164" s="56"/>
       <c r="AI164" s="56"/>
       <c r="AJ164" s="56"/>
@@ -24770,11 +25036,11 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>25.418181818181822</v>
+        <v>25.406521739130437</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24782,7 +25048,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.6202542090217413</v>
+        <v>1.6085941299703563</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24957,7 +25223,9 @@
       <c r="AF166" s="56">
         <v>16</v>
       </c>
-      <c r="AG166" s="56"/>
+      <c r="AG166" s="56">
+        <v>13.66666666666667</v>
+      </c>
       <c r="AH166" s="56"/>
       <c r="AI166" s="56"/>
       <c r="AJ166" s="56"/>
@@ -24968,11 +25236,11 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>14.963333333333335</v>
+        <v>14.901587301587304</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24980,7 +25248,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>1.364863799283194</v>
+        <v>1.303117767537163</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25076,7 +25344,9 @@
       <c r="AF167" s="56">
         <v>20.8</v>
       </c>
-      <c r="AG167" s="56"/>
+      <c r="AG167" s="56">
+        <v>19.666666666666671</v>
+      </c>
       <c r="AH167" s="56"/>
       <c r="AI167" s="56"/>
       <c r="AJ167" s="56"/>
@@ -25087,11 +25357,11 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>20.73</v>
+        <v>20.679365079365081</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25099,7 +25369,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>1.6944321903893602</v>
+        <v>1.6437972697544403</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25195,7 +25465,9 @@
       <c r="AF168" s="56">
         <v>27.2</v>
       </c>
-      <c r="AG168" s="56"/>
+      <c r="AG168" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AH168" s="56"/>
       <c r="AI168" s="56"/>
       <c r="AJ168" s="56"/>
@@ -25206,11 +25478,11 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>27.942500000000003</v>
+        <v>27.811904761904763</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25218,7 +25490,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>1.876635533933424</v>
+        <v>1.7460402958381849</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25318,7 +25590,9 @@
       <c r="AF169" s="56">
         <v>10.45</v>
       </c>
-      <c r="AG169" s="56"/>
+      <c r="AG169" s="56">
+        <v>9.85</v>
+      </c>
       <c r="AH169" s="56"/>
       <c r="AI169" s="56"/>
       <c r="AJ169" s="56"/>
@@ -25329,11 +25603,11 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>8.9522727272727263</v>
+        <v>8.9913043478260857</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25341,7 +25615,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>0.410148445918189</v>
+        <v>0.4491800664715484</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25425,7 +25699,9 @@
       <c r="AF170" s="56">
         <v>26.2</v>
       </c>
-      <c r="AG170" s="56"/>
+      <c r="AG170" s="56">
+        <v>23.466666666666669</v>
+      </c>
       <c r="AH170" s="56"/>
       <c r="AI170" s="56"/>
       <c r="AJ170" s="56"/>
@@ -25436,19 +25712,19 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ170" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ170" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>24.64</v>
       </c>
       <c r="AR170" s="71">
         <f>IFERROR(VLOOKUP(A170,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.090623941862471</v>
       </c>
-      <c r="AS170" s="71" t="str">
+      <c r="AS170" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.5493760581375291</v>
       </c>
     </row>
     <row r="171" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25546,7 +25822,9 @@
       <c r="AF171" s="56">
         <v>20.6</v>
       </c>
-      <c r="AG171" s="56"/>
+      <c r="AG171" s="56">
+        <v>19.466666666666669</v>
+      </c>
       <c r="AH171" s="56"/>
       <c r="AI171" s="56"/>
       <c r="AJ171" s="56"/>
@@ -25557,11 +25835,11 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>20.88571428571429</v>
+        <v>20.821212121212124</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25569,7 +25847,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>1.9567882634623714</v>
+        <v>1.8922860989602057</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25665,7 +25943,9 @@
       <c r="AF172" s="56">
         <v>26.7</v>
       </c>
-      <c r="AG172" s="56"/>
+      <c r="AG172" s="56">
+        <v>24.25</v>
+      </c>
       <c r="AH172" s="56"/>
       <c r="AI172" s="56"/>
       <c r="AJ172" s="56"/>
@@ -25676,11 +25956,11 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>25.697500000000002</v>
+        <v>25.62857142857143</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25688,7 +25968,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>1.2588716314881232</v>
+        <v>1.1899430600595515</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25788,7 +26068,9 @@
       <c r="AF173" s="56">
         <v>25.85</v>
       </c>
-      <c r="AG173" s="56"/>
+      <c r="AG173" s="56">
+        <v>24.35</v>
+      </c>
       <c r="AH173" s="56"/>
       <c r="AI173" s="56"/>
       <c r="AJ173" s="56"/>
@@ -25799,11 +26081,11 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>25.166287878787884</v>
+        <v>25.130797101449279</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25811,7 +26093,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>1.1118792766373531</v>
+        <v>1.0763884992987478</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25909,7 +26191,9 @@
       <c r="AF174" s="56">
         <v>15.46666666666667</v>
       </c>
-      <c r="AG174" s="56"/>
+      <c r="AG174" s="56">
+        <v>12.8</v>
+      </c>
       <c r="AH174" s="56"/>
       <c r="AI174" s="56"/>
       <c r="AJ174" s="56"/>
@@ -25920,11 +26204,11 @@
       <c r="AO174" s="56"/>
       <c r="AP174" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ174" s="71">
         <f t="shared" si="7"/>
-        <v>13.888888888888893</v>
+        <v>13.839393939393943</v>
       </c>
       <c r="AR174" s="71">
         <f>IFERROR(VLOOKUP(A174,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25932,7 +26216,7 @@
       </c>
       <c r="AS174" s="71">
         <f t="shared" si="8"/>
-        <v>1.8281370312170324</v>
+        <v>1.7786420817220829</v>
       </c>
     </row>
     <row r="175" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26299,7 +26583,9 @@
       <c r="AF178" s="56">
         <v>25.2</v>
       </c>
-      <c r="AG178" s="56"/>
+      <c r="AG178" s="56">
+        <v>24.066666666666659</v>
+      </c>
       <c r="AH178" s="56"/>
       <c r="AI178" s="56"/>
       <c r="AJ178" s="56"/>
@@ -26310,11 +26596,11 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ178" s="71">
         <f t="shared" si="7"/>
-        <v>25.286274509803917</v>
+        <v>25.218518518518515</v>
       </c>
       <c r="AR178" s="71">
         <f>IFERROR(VLOOKUP(A178,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26322,7 +26608,7 @@
       </c>
       <c r="AS178" s="71">
         <f t="shared" si="8"/>
-        <v>0.73399416292502551</v>
+        <v>0.66623817163962329</v>
       </c>
     </row>
     <row r="179" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26616,7 +26902,9 @@
       <c r="AF181" s="56">
         <v>32.4</v>
       </c>
-      <c r="AG181" s="56"/>
+      <c r="AG181" s="56">
+        <v>30.06666666666667</v>
+      </c>
       <c r="AH181" s="56"/>
       <c r="AI181" s="56"/>
       <c r="AJ181" s="56"/>
@@ -26627,11 +26915,11 @@
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ181" s="71">
         <f t="shared" si="7"/>
-        <v>30.945454545454538</v>
+        <v>30.907246376811589</v>
       </c>
       <c r="AR181" s="71">
         <f>IFERROR(VLOOKUP(A181,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26639,7 +26927,7 @@
       </c>
       <c r="AS181" s="71">
         <f t="shared" si="8"/>
-        <v>2.4122181578847268</v>
+        <v>2.3740099892417774</v>
       </c>
     </row>
     <row r="182" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26897,7 +27185,9 @@
       <c r="AF184" s="56">
         <v>28.93333333333333</v>
       </c>
-      <c r="AG184" s="56"/>
+      <c r="AG184" s="56">
+        <v>28.6</v>
+      </c>
       <c r="AH184" s="56"/>
       <c r="AI184" s="56"/>
       <c r="AJ184" s="56"/>
@@ -26908,11 +27198,11 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ184" s="71">
         <f t="shared" si="7"/>
-        <v>28.069696969696967</v>
+        <v>28.092753623188404</v>
       </c>
       <c r="AR184" s="71">
         <f>IFERROR(VLOOKUP(A184,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26920,7 +27210,7 @@
       </c>
       <c r="AS184" s="71">
         <f t="shared" si="8"/>
-        <v>1.431325752079978</v>
+        <v>1.4543824055714154</v>
       </c>
     </row>
     <row r="185" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27012,7 +27302,9 @@
       <c r="AF185" s="56">
         <v>30.733333333333331</v>
       </c>
-      <c r="AG185" s="56"/>
+      <c r="AG185" s="56">
+        <v>28.6</v>
+      </c>
       <c r="AH185" s="56"/>
       <c r="AI185" s="56"/>
       <c r="AJ185" s="56"/>
@@ -27023,11 +27315,11 @@
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ185" s="71">
         <f t="shared" si="7"/>
-        <v>28.93333333333333</v>
+        <v>28.91578947368421</v>
       </c>
       <c r="AR185" s="71">
         <f>IFERROR(VLOOKUP(A185,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27035,7 +27327,7 @@
       </c>
       <c r="AS185" s="71">
         <f t="shared" si="8"/>
-        <v>1.324701048321959</v>
+        <v>1.3071571886728393</v>
       </c>
     </row>
     <row r="186" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27293,7 +27585,9 @@
       <c r="AF188" s="56">
         <v>17.93333333333333</v>
       </c>
-      <c r="AG188" s="56"/>
+      <c r="AG188" s="56">
+        <v>16.133333333333329</v>
+      </c>
       <c r="AH188" s="56"/>
       <c r="AI188" s="56"/>
       <c r="AJ188" s="56"/>
@@ -27304,11 +27598,11 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>17.45454545454546</v>
+        <v>17.397101449275368</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27316,7 +27610,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.4589534650137299</v>
+        <v>1.4015094597436377</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27404,7 +27698,9 @@
       <c r="AF189" s="56">
         <v>33.266666666666673</v>
       </c>
-      <c r="AG189" s="56"/>
+      <c r="AG189" s="56">
+        <v>29.533333333333331</v>
+      </c>
       <c r="AH189" s="56"/>
       <c r="AI189" s="56"/>
       <c r="AJ189" s="56"/>
@@ -27415,11 +27711,11 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ189" s="71">
         <f t="shared" si="7"/>
-        <v>32.225000000000009</v>
+        <v>32.06666666666667</v>
       </c>
       <c r="AR189" s="71">
         <f>IFERROR(VLOOKUP(A189,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27427,7 +27723,7 @@
       </c>
       <c r="AS189" s="71">
         <f t="shared" si="8"/>
-        <v>2.3734156419472185</v>
+        <v>2.21508230861388</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27527,7 +27823,9 @@
       <c r="AF190" s="56">
         <v>30.933333333333341</v>
       </c>
-      <c r="AG190" s="56"/>
+      <c r="AG190" s="56">
+        <v>27.8</v>
+      </c>
       <c r="AH190" s="56"/>
       <c r="AI190" s="56"/>
       <c r="AJ190" s="56"/>
@@ -27538,11 +27836,11 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>30.733333333333338</v>
+        <v>30.605797101449276</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27550,7 +27848,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>1.8168096718508693</v>
+        <v>1.6892734399668079</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27650,7 +27948,9 @@
       <c r="AF191" s="56">
         <v>19.149999999999999</v>
       </c>
-      <c r="AG191" s="56"/>
+      <c r="AG191" s="56">
+        <v>17.7</v>
+      </c>
       <c r="AH191" s="56"/>
       <c r="AI191" s="56"/>
       <c r="AJ191" s="56"/>
@@ -27661,11 +27961,11 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>18.727272727272723</v>
+        <v>18.682608695652171</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27673,7 +27973,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>1.3400537126121144</v>
+        <v>1.2953896809915619</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27773,7 +28073,9 @@
       <c r="AF192" s="56">
         <v>26.13333333333334</v>
       </c>
-      <c r="AG192" s="56"/>
+      <c r="AG192" s="56">
+        <v>26.333333333333329</v>
+      </c>
       <c r="AH192" s="56"/>
       <c r="AI192" s="56"/>
       <c r="AJ192" s="56"/>
@@ -27784,11 +28086,11 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>26.106060606060613</v>
+        <v>26.115942028985515</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27796,7 +28098,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>0.86155342524244105</v>
+        <v>0.87143484816734329</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27887,8 +28189,12 @@
       </c>
       <c r="AD193" s="56"/>
       <c r="AE193" s="56"/>
-      <c r="AF193" s="56"/>
-      <c r="AG193" s="56"/>
+      <c r="AF193" s="56">
+        <v>28.05</v>
+      </c>
+      <c r="AG193" s="56">
+        <v>26.5</v>
+      </c>
       <c r="AH193" s="56"/>
       <c r="AI193" s="56"/>
       <c r="AJ193" s="56"/>
@@ -27899,11 +28205,11 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ193" s="71">
         <f t="shared" si="7"/>
-        <v>27.008333333333329</v>
+        <v>27.034999999999997</v>
       </c>
       <c r="AR193" s="71">
         <f>IFERROR(VLOOKUP(A193,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27911,7 +28217,7 @@
       </c>
       <c r="AS193" s="71">
         <f t="shared" si="8"/>
-        <v>0.65556379332415915</v>
+        <v>0.68223045999082643</v>
       </c>
     </row>
     <row r="194" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28011,7 +28317,9 @@
       <c r="AF194" s="56">
         <v>22.666666666666671</v>
       </c>
-      <c r="AG194" s="56"/>
+      <c r="AG194" s="56">
+        <v>20.666666666666671</v>
+      </c>
       <c r="AH194" s="56"/>
       <c r="AI194" s="56"/>
       <c r="AJ194" s="56"/>
@@ -28022,11 +28330,11 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>21.242424242424246</v>
+        <v>21.217391304347828</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28034,7 +28342,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>-0.36523755463418439</v>
+        <v>-0.39027049271060221</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28134,7 +28442,9 @@
       <c r="AF195" s="56">
         <v>27.13333333333334</v>
       </c>
-      <c r="AG195" s="56"/>
+      <c r="AG195" s="56">
+        <v>25.06666666666667</v>
+      </c>
       <c r="AH195" s="56"/>
       <c r="AI195" s="56"/>
       <c r="AJ195" s="56"/>
@@ -28145,11 +28455,11 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>27.930303030303026</v>
+        <v>27.805797101449276</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28157,7 +28467,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>2.2428148205932672</v>
+        <v>2.1183088917395168</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28257,7 +28567,9 @@
       <c r="AF196" s="56">
         <v>22.4</v>
       </c>
-      <c r="AG196" s="56"/>
+      <c r="AG196" s="56">
+        <v>20.533333333333331</v>
+      </c>
       <c r="AH196" s="56"/>
       <c r="AI196" s="56"/>
       <c r="AJ196" s="56"/>
@@ -28268,11 +28580,11 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>22.327272727272728</v>
+        <v>22.249275362318841</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28280,7 +28592,7 @@
       </c>
       <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v>2.1035162557474578</v>
+        <v>2.0255188907935704</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28380,7 +28692,9 @@
       <c r="AF197" s="56">
         <v>27.2</v>
       </c>
-      <c r="AG197" s="56"/>
+      <c r="AG197" s="56">
+        <v>22.933333333333341</v>
+      </c>
       <c r="AH197" s="56"/>
       <c r="AI197" s="56"/>
       <c r="AJ197" s="56"/>
@@ -28391,11 +28705,11 @@
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ197" s="71">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>25.957575757575754</v>
+        <v>25.826086956521738</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28403,7 +28717,7 @@
       </c>
       <c r="AS197" s="71">
         <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>1.8301927564052249</v>
+        <v>1.6987039553512098</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28503,7 +28817,9 @@
       <c r="AF198" s="56">
         <v>21.45</v>
       </c>
-      <c r="AG198" s="56"/>
+      <c r="AG198" s="56">
+        <v>19.600000000000001</v>
+      </c>
       <c r="AH198" s="56"/>
       <c r="AI198" s="56"/>
       <c r="AJ198" s="56"/>
@@ -28514,11 +28830,11 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>21.688636363636359</v>
+        <v>21.597826086956516</v>
       </c>
       <c r="AR198" s="71" t="str">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28626,7 +28942,9 @@
       <c r="AF199" s="56">
         <v>16.866666666666671</v>
       </c>
-      <c r="AG199" s="56"/>
+      <c r="AG199" s="56">
+        <v>16.06666666666667</v>
+      </c>
       <c r="AH199" s="56"/>
       <c r="AI199" s="56"/>
       <c r="AJ199" s="56"/>
@@ -28637,11 +28955,11 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>16.636363636363637</v>
+        <v>16.611594202898551</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28649,7 +28967,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>0.84870323017244687</v>
+        <v>0.82393379670736167</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28749,7 +29067,9 @@
       <c r="AF200" s="56">
         <v>15.65</v>
       </c>
-      <c r="AG200" s="56"/>
+      <c r="AG200" s="56">
+        <v>14.4</v>
+      </c>
       <c r="AH200" s="56"/>
       <c r="AI200" s="56"/>
       <c r="AJ200" s="56"/>
@@ -28760,11 +29080,11 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>14.765909090909094</v>
+        <v>14.750000000000002</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28772,7 +29092,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>1.4002966231254543</v>
+        <v>1.3843875322163619</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28872,7 +29192,9 @@
       <c r="AF201" s="56">
         <v>29.2</v>
       </c>
-      <c r="AG201" s="56"/>
+      <c r="AG201" s="56">
+        <v>24.15</v>
+      </c>
       <c r="AH201" s="56"/>
       <c r="AI201" s="56"/>
       <c r="AJ201" s="56"/>
@@ -28883,11 +29205,11 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ201" s="71">
         <f t="shared" si="10"/>
-        <v>27.270454545454541</v>
+        <v>27.134782608695648</v>
       </c>
       <c r="AR201" s="71">
         <f>IFERROR(VLOOKUP(A201,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28895,7 +29217,7 @@
       </c>
       <c r="AS201" s="71">
         <f t="shared" si="11"/>
-        <v>1.7329252771236909</v>
+        <v>1.5972533403647979</v>
       </c>
     </row>
     <row r="202" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29102,7 +29424,9 @@
       <c r="AF203" s="56">
         <v>15.2</v>
       </c>
-      <c r="AG203" s="56"/>
+      <c r="AG203" s="56">
+        <v>13.133333333333329</v>
+      </c>
       <c r="AH203" s="56"/>
       <c r="AI203" s="56"/>
       <c r="AJ203" s="56"/>
@@ -29113,11 +29437,11 @@
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ203" s="71">
         <f t="shared" si="10"/>
-        <v>14.12</v>
+        <v>14.073015873015871</v>
       </c>
       <c r="AR203" s="71">
         <f>IFERROR(VLOOKUP(A203,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29125,7 +29449,7 @@
       </c>
       <c r="AS203" s="71">
         <f t="shared" si="11"/>
-        <v>2.1491251495189587</v>
+        <v>2.1021410225348305</v>
       </c>
     </row>
     <row r="204" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29323,8 +29647,12 @@
       <c r="AE205" s="56">
         <v>15.8</v>
       </c>
-      <c r="AF205" s="56"/>
-      <c r="AG205" s="56"/>
+      <c r="AF205" s="56">
+        <v>14.35</v>
+      </c>
+      <c r="AG205" s="56">
+        <v>14.85</v>
+      </c>
       <c r="AH205" s="56"/>
       <c r="AI205" s="56"/>
       <c r="AJ205" s="56"/>
@@ -29335,11 +29663,11 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ205" s="71">
         <f t="shared" si="10"/>
-        <v>14.419047619047618</v>
+        <v>14.434782608695652</v>
       </c>
       <c r="AR205" s="71">
         <f>IFERROR(VLOOKUP(A205,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29347,7 +29675,7 @@
       </c>
       <c r="AS205" s="71">
         <f t="shared" si="11"/>
-        <v>1.004153502229947</v>
+        <v>1.0198884918779818</v>
       </c>
     </row>
     <row r="206" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29554,7 +29882,9 @@
       <c r="AF207" s="56">
         <v>14.2</v>
       </c>
-      <c r="AG207" s="56"/>
+      <c r="AG207" s="56">
+        <v>14.06666666666667</v>
+      </c>
       <c r="AH207" s="56"/>
       <c r="AI207" s="56"/>
       <c r="AJ207" s="56"/>
@@ -29565,11 +29895,11 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ207" s="71">
         <f t="shared" si="10"/>
-        <v>14.293333333333331</v>
+        <v>14.279166666666665</v>
       </c>
       <c r="AR207" s="71">
         <f>IFERROR(VLOOKUP(A207,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29577,7 +29907,7 @@
       </c>
       <c r="AS207" s="71">
         <f t="shared" si="11"/>
-        <v>0.73255752827061116</v>
+        <v>0.71839086160394494</v>
       </c>
     </row>
     <row r="208" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29675,7 +30005,9 @@
       <c r="AF208" s="56">
         <v>14.15</v>
       </c>
-      <c r="AG208" s="56"/>
+      <c r="AG208" s="56">
+        <v>14.65</v>
+      </c>
       <c r="AH208" s="56"/>
       <c r="AI208" s="56"/>
       <c r="AJ208" s="56"/>
@@ -29686,11 +30018,11 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v>14.397619047619045</v>
+        <v>14.409090909090907</v>
       </c>
       <c r="AR208" s="71" t="str">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29798,7 +30130,9 @@
       <c r="AF209" s="56">
         <v>11.05</v>
       </c>
-      <c r="AG209" s="56"/>
+      <c r="AG209" s="56">
+        <v>11.6</v>
+      </c>
       <c r="AH209" s="56"/>
       <c r="AI209" s="56"/>
       <c r="AJ209" s="56"/>
@@ -29809,11 +30143,11 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>11.045454545454547</v>
+        <v>11.069565217391306</v>
       </c>
       <c r="AR209" s="71" t="str">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29921,7 +30255,9 @@
       <c r="AF210" s="56">
         <v>16.45</v>
       </c>
-      <c r="AG210" s="56"/>
+      <c r="AG210" s="56">
+        <v>14.95</v>
+      </c>
       <c r="AH210" s="56"/>
       <c r="AI210" s="56"/>
       <c r="AJ210" s="56"/>
@@ -29932,11 +30268,11 @@
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ210" s="71">
         <f t="shared" si="10"/>
-        <v>15.786363636363637</v>
+        <v>15.75</v>
       </c>
       <c r="AR210" s="71">
         <f>IFERROR(VLOOKUP(A210,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29944,7 +30280,7 @@
       </c>
       <c r="AS210" s="71">
         <f t="shared" si="11"/>
-        <v>1.4566934310797066</v>
+        <v>1.4203297947160696</v>
       </c>
     </row>
     <row r="211" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30044,7 +30380,9 @@
       <c r="AF211" s="56">
         <v>8.85</v>
       </c>
-      <c r="AG211" s="56"/>
+      <c r="AG211" s="56">
+        <v>8.1</v>
+      </c>
       <c r="AH211" s="56"/>
       <c r="AI211" s="56"/>
       <c r="AJ211" s="56"/>
@@ -30055,11 +30393,11 @@
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ211" s="71">
         <f t="shared" si="10"/>
-        <v>8.6749999999999989</v>
+        <v>8.6499999999999986</v>
       </c>
       <c r="AR211" s="71">
         <f>IFERROR(VLOOKUP(A211,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30067,7 +30405,7 @@
       </c>
       <c r="AS211" s="71">
         <f t="shared" si="11"/>
-        <v>0.59486711830959926</v>
+        <v>0.56986711830959891</v>
       </c>
     </row>
     <row r="212" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30164,8 +30502,12 @@
       <c r="AE212" s="56">
         <v>24.15</v>
       </c>
-      <c r="AF212" s="56"/>
-      <c r="AG212" s="56"/>
+      <c r="AF212" s="56">
+        <v>27.15</v>
+      </c>
+      <c r="AG212" s="56">
+        <v>26.75</v>
+      </c>
       <c r="AH212" s="56"/>
       <c r="AI212" s="56"/>
       <c r="AJ212" s="56"/>
@@ -30176,11 +30518,11 @@
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ212" s="71">
         <f t="shared" si="10"/>
-        <v>25.352380952380948</v>
+        <v>25.49130434782608</v>
       </c>
       <c r="AR212" s="71" t="str">
         <f>IFERROR(VLOOKUP(A212,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30192,7 +30534,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="AF1:AF212" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="AF1:AF212" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="K5:AO212">
     <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>""</formula>
